--- a/plot/sensitivity_theta.xlsx
+++ b/plot/sensitivity_theta.xlsx
@@ -436,32 +436,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Unit Cost (元/kWh)</t>
+          <t>LCOE (元/kWh)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Investment Cost (万元)</t>
+          <t>Equipment Investment (万元, one-time)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Grid Cost (万元)</t>
+          <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Connection Cost (万元)</t>
+          <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Market Revenue (万元)</t>
+          <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Objective (万元)</t>
+          <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -490,34 +490,34 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03479157580945485</v>
+        <v>0.2012387270137435</v>
       </c>
       <c r="C2" t="n">
-        <v>9729.535926229004</v>
+        <v>167893.785397132</v>
       </c>
       <c r="D2" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>5000</v>
       </c>
       <c r="F2" t="n">
-        <v>5182.024771742844</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>21296.79514230655</v>
+        <v>20728.08482641648</v>
       </c>
       <c r="H2" t="n">
-        <v>123.0087649383532</v>
+        <v>86.94754087686988</v>
       </c>
       <c r="I2" t="n">
-        <v>63.50422172258834</v>
+        <v>143.8317550123589</v>
       </c>
       <c r="J2" t="n">
-        <v>67.07219964490221</v>
+        <v>483.8382291153493</v>
       </c>
       <c r="K2" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>0.2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03377456124260887</v>
+        <v>0.2011212020879527</v>
       </c>
       <c r="C3" t="n">
-        <v>14728.45659747047</v>
+        <v>167792.8141298217</v>
       </c>
       <c r="D3" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>5000</v>
       </c>
       <c r="F3" t="n">
-        <v>5731.487880758592</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>25746.25270453135</v>
+        <v>20718.62596137552</v>
       </c>
       <c r="H3" t="n">
-        <v>200.945987730557</v>
+        <v>74.78175886784811</v>
       </c>
       <c r="I3" t="n">
-        <v>89.70942402075013</v>
+        <v>158.6441210180144</v>
       </c>
       <c r="J3" t="n">
-        <v>58.66196621317401</v>
+        <v>502.2034833580568</v>
       </c>
       <c r="K3" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>0.3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03379929626867933</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C4" t="n">
-        <v>13106.53760906378</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D4" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>5000</v>
       </c>
       <c r="F4" t="n">
-        <v>5658.110705119165</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>24197.71089176456</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H4" t="n">
-        <v>187.7217931756649</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I4" t="n">
-        <v>50.68883957922867</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J4" t="n">
-        <v>74.17576533402961</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K4" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>0.4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03521043412680988</v>
+        <v>0.2012857605490734</v>
       </c>
       <c r="C5" t="n">
-        <v>10256.83988517803</v>
+        <v>167934.1941498828</v>
       </c>
       <c r="D5" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>5000</v>
       </c>
       <c r="F5" t="n">
-        <v>5059.172469494792</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>21946.95140350337</v>
+        <v>20731.87026903719</v>
       </c>
       <c r="H5" t="n">
-        <v>137.9415576606542</v>
+        <v>86.94754087686988</v>
       </c>
       <c r="I5" t="n">
-        <v>56.00937432727414</v>
+        <v>143.9879581303967</v>
       </c>
       <c r="J5" t="n">
-        <v>59.85640184724372</v>
+        <v>483.7952145642791</v>
       </c>
       <c r="K5" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03374727508882829</v>
+        <v>0.2015855026961427</v>
       </c>
       <c r="C6" t="n">
-        <v>13680.44305632515</v>
+        <v>168191.7169200718</v>
       </c>
       <c r="D6" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>5000</v>
       </c>
       <c r="F6" t="n">
-        <v>5698.944473397137</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>24730.78257074793</v>
+        <v>20755.99468772657</v>
       </c>
       <c r="H6" t="n">
-        <v>201.316425555707</v>
+        <v>86.94754087686806</v>
       </c>
       <c r="I6" t="n">
-        <v>50.84921854256438</v>
+        <v>144.9834320545083</v>
       </c>
       <c r="J6" t="n">
-        <v>60.31855924003579</v>
+        <v>483.5210851839897</v>
       </c>
       <c r="K6" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>0.6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03422192590174921</v>
+        <v>0.1986201916340543</v>
       </c>
       <c r="C7" t="n">
-        <v>15830.12155505829</v>
+        <v>165644.0768012321</v>
       </c>
       <c r="D7" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>5000</v>
       </c>
       <c r="F7" t="n">
-        <v>5621.813555494467</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>26957.59198738306</v>
+        <v>20517.33487192986</v>
       </c>
       <c r="H7" t="n">
-        <v>235.9670033173185</v>
+        <v>76.98933608601322</v>
       </c>
       <c r="I7" t="n">
-        <v>56.32175217496615</v>
+        <v>147.5793668631472</v>
       </c>
       <c r="J7" t="n">
-        <v>63.75342660476856</v>
+        <v>501.1777672711996</v>
       </c>
       <c r="K7" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>0.7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03355272980687543</v>
+        <v>0.201585502696143</v>
       </c>
       <c r="C8" t="n">
-        <v>14433.79940900475</v>
+        <v>168191.716920072</v>
       </c>
       <c r="D8" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>5000</v>
       </c>
       <c r="F8" t="n">
-        <v>5795.935978545636</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>25387.14741827879</v>
+        <v>20755.9946877266</v>
       </c>
       <c r="H8" t="n">
-        <v>202.3130188690819</v>
+        <v>86.94754087686852</v>
       </c>
       <c r="I8" t="n">
-        <v>77.99552356886245</v>
+        <v>144.9834320545087</v>
       </c>
       <c r="J8" t="n">
-        <v>55.65231230131445</v>
+        <v>483.5210851839887</v>
       </c>
       <c r="K8" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>0.8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03372653932642238</v>
+        <v>0.1985977514713174</v>
       </c>
       <c r="C9" t="n">
-        <v>16464.57176307647</v>
+        <v>165624.7973874826</v>
       </c>
       <c r="D9" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>5000</v>
       </c>
       <c r="F9" t="n">
-        <v>5817.435654531051</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>27396.42009636476</v>
+        <v>20515.52879998897</v>
       </c>
       <c r="H9" t="n">
-        <v>232.1451809679292</v>
+        <v>79.00706671703624</v>
       </c>
       <c r="I9" t="n">
-        <v>81.21395526045956</v>
+        <v>144.9834320545092</v>
       </c>
       <c r="J9" t="n">
-        <v>74.40706965399016</v>
+        <v>498.1701849393872</v>
       </c>
       <c r="K9" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -770,34 +770,34 @@
         <v>0.9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03328518483474904</v>
+        <v>0.2012196776768663</v>
       </c>
       <c r="C10" t="n">
-        <v>14416.33532064578</v>
+        <v>167877.4192035525</v>
       </c>
       <c r="D10" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>5000</v>
       </c>
       <c r="F10" t="n">
-        <v>5887.181671827696</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>25278.43763663777</v>
+        <v>20726.55166138422</v>
       </c>
       <c r="H10" t="n">
-        <v>196.1624666260826</v>
+        <v>85.97529657203813</v>
       </c>
       <c r="I10" t="n">
-        <v>80.03256288181076</v>
+        <v>144.9834320545087</v>
       </c>
       <c r="J10" t="n">
-        <v>74.93760775028331</v>
+        <v>485.3147442931798</v>
       </c>
       <c r="K10" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_theta.xlsx
+++ b/plot/sensitivity_theta.xlsx
@@ -490,34 +490,34 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2012387270137435</v>
+        <v>0.3134539627960541</v>
       </c>
       <c r="C2" t="n">
-        <v>167893.785397132</v>
+        <v>34608.41097909577</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>9501.40767655602</v>
       </c>
       <c r="E2" t="n">
         <v>5000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>313.6143214699795</v>
       </c>
       <c r="G2" t="n">
-        <v>20728.08482641648</v>
+        <v>17429.86704053646</v>
       </c>
       <c r="H2" t="n">
-        <v>86.94754087686988</v>
+        <v>4.704317183466853</v>
       </c>
       <c r="I2" t="n">
-        <v>143.8317550123589</v>
+        <v>50.73767761128007</v>
       </c>
       <c r="J2" t="n">
-        <v>483.8382291153493</v>
+        <v>107.8862316534596</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>31.79855313439097</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>0.2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2011212020879527</v>
+        <v>0.3122002594179608</v>
       </c>
       <c r="C3" t="n">
-        <v>167792.8141298217</v>
+        <v>34474.16064924459</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9502.25797014053</v>
       </c>
       <c r="E3" t="n">
         <v>5000</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>352.1792557976401</v>
       </c>
       <c r="G3" t="n">
-        <v>20718.62596137552</v>
+        <v>17379.57599280553</v>
       </c>
       <c r="H3" t="n">
-        <v>74.78175886784811</v>
+        <v>4.687554505003214</v>
       </c>
       <c r="I3" t="n">
-        <v>158.6441210180144</v>
+        <v>50.25512957798401</v>
       </c>
       <c r="J3" t="n">
-        <v>502.2034833580568</v>
+        <v>108.0231485793203</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>31.80139882911825</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>0.3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C4" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E4" t="n">
         <v>5000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G4" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H4" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I4" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J4" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>0.4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2012857605490734</v>
+        <v>0.3126293849463789</v>
       </c>
       <c r="C5" t="n">
-        <v>167934.1941498828</v>
+        <v>37550.12301127485</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9502.805537220916</v>
       </c>
       <c r="E5" t="n">
         <v>5000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>461.0180292761237</v>
       </c>
       <c r="G5" t="n">
-        <v>20731.87026903719</v>
+        <v>17559.43718489223</v>
       </c>
       <c r="H5" t="n">
-        <v>86.94754087686988</v>
+        <v>4.67675977354459</v>
       </c>
       <c r="I5" t="n">
-        <v>143.9879581303967</v>
+        <v>61.58552179614693</v>
       </c>
       <c r="J5" t="n">
-        <v>483.7952145642791</v>
+        <v>105.911812211392</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>31.8032313829348</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2015855026961427</v>
+        <v>0.306780050109968</v>
       </c>
       <c r="C6" t="n">
-        <v>168191.7169200718</v>
+        <v>40522.10351429378</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9628.45674430799</v>
       </c>
       <c r="E6" t="n">
         <v>5000</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>906.5661546039224</v>
       </c>
       <c r="G6" t="n">
-        <v>20755.99468772657</v>
+        <v>17517.95177154058</v>
       </c>
       <c r="H6" t="n">
-        <v>86.94754087686806</v>
+        <v>4.580825333500402</v>
       </c>
       <c r="I6" t="n">
-        <v>144.9834320545083</v>
+        <v>75.15318397140169</v>
       </c>
       <c r="J6" t="n">
-        <v>483.5210851839897</v>
+        <v>98.93978741974308</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>32.22375081763049</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>0.6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1986201916340543</v>
+        <v>0.3033902883800229</v>
       </c>
       <c r="C7" t="n">
-        <v>165644.0768012321</v>
+        <v>40375.71491667494</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9561.551115853958</v>
       </c>
       <c r="E7" t="n">
         <v>5000</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>950.2972192576518</v>
       </c>
       <c r="G7" t="n">
-        <v>20517.33487192986</v>
+        <v>17393.60157334075</v>
       </c>
       <c r="H7" t="n">
-        <v>76.98933608601322</v>
+        <v>5.029127217089584</v>
       </c>
       <c r="I7" t="n">
-        <v>147.5793668631472</v>
+        <v>72.3790494674473</v>
       </c>
       <c r="J7" t="n">
-        <v>501.1777672711996</v>
+        <v>101.7368380627048</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>31.99983639844029</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>0.7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.201585502696143</v>
+        <v>0.3094920022988774</v>
       </c>
       <c r="C8" t="n">
-        <v>168191.716920072</v>
+        <v>40081.93720908157</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>9502.805537220918</v>
       </c>
       <c r="E8" t="n">
         <v>5000</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>670.1095980765814</v>
       </c>
       <c r="G8" t="n">
-        <v>20755.9946877266</v>
+        <v>17587.52287892875</v>
       </c>
       <c r="H8" t="n">
-        <v>86.94754087686852</v>
+        <v>4.676759773544582</v>
       </c>
       <c r="I8" t="n">
-        <v>144.9834320545087</v>
+        <v>67.82323299353823</v>
       </c>
       <c r="J8" t="n">
-        <v>483.5210851839887</v>
+        <v>110.3151511353209</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>31.8032313829348</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>0.8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1985977514713174</v>
+        <v>0.3121311272093377</v>
       </c>
       <c r="C9" t="n">
-        <v>165624.7973874826</v>
+        <v>38572.93487042869</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9503.147951548766</v>
       </c>
       <c r="E9" t="n">
         <v>5000</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>519.3959971187203</v>
       </c>
       <c r="G9" t="n">
-        <v>20515.52879998897</v>
+        <v>17597.21739754289</v>
       </c>
       <c r="H9" t="n">
-        <v>79.00706671703624</v>
+        <v>4.672855992181227</v>
       </c>
       <c r="I9" t="n">
-        <v>144.9834320545092</v>
+        <v>65.00795947389395</v>
       </c>
       <c r="J9" t="n">
-        <v>498.1701849393872</v>
+        <v>105.9012060318475</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>31.80437734788744</v>
       </c>
     </row>
     <row r="10">
@@ -770,34 +770,34 @@
         <v>0.9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2012196776768663</v>
+        <v>0.2462838011099229</v>
       </c>
       <c r="C10" t="n">
-        <v>167877.4192035525</v>
+        <v>77473.71889104311</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>6341.6286038549</v>
       </c>
       <c r="E10" t="n">
         <v>5000</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1176.81110778884</v>
       </c>
       <c r="G10" t="n">
-        <v>20726.55166138422</v>
+        <v>17422.46089039437</v>
       </c>
       <c r="H10" t="n">
-        <v>85.97529657203813</v>
+        <v>36.72535831533005</v>
       </c>
       <c r="I10" t="n">
-        <v>144.9834320545087</v>
+        <v>74.66324541881465</v>
       </c>
       <c r="J10" t="n">
-        <v>485.3147442931798</v>
+        <v>218.5656426435187</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>21.2236566394073</v>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_theta.xlsx
+++ b/plot/sensitivity_theta.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theta Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="theta Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,379 +425,557 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Distance (km)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Min Self-consumption Ratio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Min RE Generation Ratio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LCOE (元/kWh)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Equipment Investment (万元, one-time)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MIP Gap Target</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MIP Gap Achieved</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Wind (MW)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PV (MW)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Storage (MWh)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Grid (MW)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Output Directory</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.1</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.3134539627960541</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34608.41097909577</v>
-      </c>
       <c r="D2" t="n">
-        <v>9501.40767655602</v>
+        <v>0.3021709655666015</v>
       </c>
       <c r="E2" t="n">
+        <v>31645.82756545992</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9779.512720130722</v>
+      </c>
+      <c r="G2" t="n">
         <v>5000</v>
       </c>
-      <c r="F2" t="n">
-        <v>313.6143214699795</v>
-      </c>
-      <c r="G2" t="n">
-        <v>17429.86704053646</v>
-      </c>
       <c r="H2" t="n">
-        <v>4.704317183466853</v>
+        <v>860.9664641283048</v>
       </c>
       <c r="I2" t="n">
-        <v>50.73767761128007</v>
+        <v>16883.08874442382</v>
       </c>
       <c r="J2" t="n">
-        <v>107.8862316534596</v>
+        <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>31.79855313439097</v>
+        <v>0.009684058484656543</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.651018313411994</v>
+      </c>
+      <c r="M2" t="n">
+        <v>49.20336046873206</v>
+      </c>
+      <c r="N2" t="n">
+        <v>91.34304614618944</v>
+      </c>
+      <c r="O2" t="n">
+        <v>32.72929290539064</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.3122002594179608</v>
-      </c>
-      <c r="C3" t="n">
-        <v>34474.16064924459</v>
-      </c>
       <c r="D3" t="n">
-        <v>9502.25797014053</v>
+        <v>0.3017438238319078</v>
       </c>
       <c r="E3" t="n">
+        <v>31641.78122526611</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9779.956226864666</v>
+      </c>
+      <c r="G3" t="n">
         <v>5000</v>
       </c>
-      <c r="F3" t="n">
-        <v>352.1792557976401</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17379.57599280553</v>
-      </c>
       <c r="H3" t="n">
-        <v>4.687554505003214</v>
+        <v>875.9272304665869</v>
       </c>
       <c r="I3" t="n">
-        <v>50.25512957798401</v>
+        <v>16868.19242861049</v>
       </c>
       <c r="J3" t="n">
-        <v>108.0231485793203</v>
+        <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>31.80139882911825</v>
+        <v>0.008813266466412136</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.65102324378649</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49.20350239966614</v>
+      </c>
+      <c r="N3" t="n">
+        <v>91.31564821809512</v>
+      </c>
+      <c r="O3" t="n">
+        <v>32.73077719834226</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.2</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.2482182265340659</v>
-      </c>
-      <c r="C4" t="n">
-        <v>76260.24694757526</v>
-      </c>
       <c r="D4" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E4" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G4" t="n">
         <v>5000</v>
       </c>
-      <c r="F4" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H4" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I4" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J4" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M4" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N4" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O4" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.3</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.3126293849463789</v>
-      </c>
-      <c r="C5" t="n">
-        <v>37550.12301127485</v>
-      </c>
       <c r="D5" t="n">
-        <v>9502.805537220916</v>
+        <v>0.292247893233171</v>
       </c>
       <c r="E5" t="n">
+        <v>37550.12301126753</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9502.805537220844</v>
+      </c>
+      <c r="G5" t="n">
         <v>5000</v>
       </c>
-      <c r="F5" t="n">
-        <v>461.0180292761237</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17559.43718489223</v>
-      </c>
       <c r="H5" t="n">
-        <v>4.67675977354459</v>
+        <v>1161.446481915717</v>
       </c>
       <c r="I5" t="n">
-        <v>61.58552179614693</v>
+        <v>16859.00873225188</v>
       </c>
       <c r="J5" t="n">
-        <v>105.911812211392</v>
+        <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>31.8032313829348</v>
+        <v>0.008273709378654355</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.676759773541903</v>
+      </c>
+      <c r="M5" t="n">
+        <v>61.58552179614139</v>
+      </c>
+      <c r="N5" t="n">
+        <v>105.911812211365</v>
+      </c>
+      <c r="O5" t="n">
+        <v>31.80323138293456</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.4</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.306780050109968</v>
-      </c>
-      <c r="C6" t="n">
-        <v>40522.10351429378</v>
-      </c>
       <c r="D6" t="n">
-        <v>9628.45674430799</v>
+        <v>0.3020527956578568</v>
       </c>
       <c r="E6" t="n">
+        <v>31372.57958274427</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9800.026448021676</v>
+      </c>
+      <c r="G6" t="n">
         <v>5000</v>
       </c>
-      <c r="F6" t="n">
-        <v>906.5661546039224</v>
-      </c>
-      <c r="G6" t="n">
-        <v>17517.95177154058</v>
-      </c>
       <c r="H6" t="n">
-        <v>4.580825333500402</v>
+        <v>874.611288827379</v>
       </c>
       <c r="I6" t="n">
-        <v>75.15318397140169</v>
+        <v>16864.36011021649</v>
       </c>
       <c r="J6" t="n">
-        <v>98.93978741974308</v>
+        <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>32.22375081763049</v>
+        <v>0.008588460215499289</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.639831277408183</v>
+      </c>
+      <c r="M6" t="n">
+        <v>48.88131872381109</v>
+      </c>
+      <c r="N6" t="n">
+        <v>90.20473226531821</v>
+      </c>
+      <c r="O6" t="n">
+        <v>32.79794661319169</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.5</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B7" t="n">
         <v>0.6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.3033902883800229</v>
-      </c>
       <c r="C7" t="n">
-        <v>40375.71491667494</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>9561.551115853958</v>
+        <v>0.2814912660214979</v>
       </c>
       <c r="E7" t="n">
+        <v>44285.74422141934</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9136.141490533599</v>
+      </c>
+      <c r="G7" t="n">
         <v>5000</v>
       </c>
-      <c r="F7" t="n">
-        <v>950.2972192576518</v>
-      </c>
-      <c r="G7" t="n">
-        <v>17393.60157334075</v>
-      </c>
       <c r="H7" t="n">
-        <v>5.029127217089584</v>
+        <v>1433.868536084216</v>
       </c>
       <c r="I7" t="n">
-        <v>72.3790494674473</v>
+        <v>16850.90740251968</v>
       </c>
       <c r="J7" t="n">
-        <v>101.7368380627048</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>31.99983639844029</v>
+        <v>0.007794040982033943</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11.45342611255706</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67.84627905306724</v>
+      </c>
+      <c r="N7" t="n">
+        <v>111.2859435006139</v>
+      </c>
+      <c r="O7" t="n">
+        <v>30.57610940606961</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.6</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.3094920022988774</v>
-      </c>
-      <c r="C8" t="n">
-        <v>40081.93720908157</v>
-      </c>
       <c r="D8" t="n">
-        <v>9502.805537220918</v>
+        <v>0.2865833899516972</v>
       </c>
       <c r="E8" t="n">
+        <v>41682.42977334704</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9336.169794196723</v>
+      </c>
+      <c r="G8" t="n">
         <v>5000</v>
       </c>
-      <c r="F8" t="n">
-        <v>670.1095980765814</v>
-      </c>
-      <c r="G8" t="n">
-        <v>17587.52287892875</v>
-      </c>
       <c r="H8" t="n">
-        <v>4.676759773544582</v>
+        <v>1354.768803431721</v>
       </c>
       <c r="I8" t="n">
-        <v>67.82323299353823</v>
+        <v>16886.16011985155</v>
       </c>
       <c r="J8" t="n">
-        <v>110.3151511353209</v>
+        <v>0.01</v>
       </c>
       <c r="K8" t="n">
-        <v>31.8032313829348</v>
+        <v>0.009867081164896955</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.2918222755351</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67.54766614801947</v>
+      </c>
+      <c r="N8" t="n">
+        <v>107.1205999035996</v>
+      </c>
+      <c r="O8" t="n">
+        <v>31.24554817334914</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.7</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.3121311272093377</v>
-      </c>
-      <c r="C9" t="n">
-        <v>38572.93487042869</v>
-      </c>
       <c r="D9" t="n">
-        <v>9503.147951548766</v>
+        <v>0.2936103895698572</v>
       </c>
       <c r="E9" t="n">
+        <v>37214.87802743564</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9611.246169937953</v>
+      </c>
+      <c r="G9" t="n">
         <v>5000</v>
       </c>
-      <c r="F9" t="n">
-        <v>519.3959971187203</v>
-      </c>
-      <c r="G9" t="n">
-        <v>17597.21739754289</v>
-      </c>
       <c r="H9" t="n">
-        <v>4.672855992181227</v>
+        <v>1209.653892624262</v>
       </c>
       <c r="I9" t="n">
-        <v>65.00795947389395</v>
+        <v>16887.83661349177</v>
       </c>
       <c r="J9" t="n">
-        <v>105.9012060318475</v>
+        <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>31.80437734788744</v>
+        <v>0.009966633872160447</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.946976159499966</v>
+      </c>
+      <c r="M9" t="n">
+        <v>64.17615919701133</v>
+      </c>
+      <c r="N9" t="n">
+        <v>101.3856716703093</v>
+      </c>
+      <c r="O9" t="n">
+        <v>32.16615184048846</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.8</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.2462838011099229</v>
-      </c>
-      <c r="C10" t="n">
-        <v>77473.71889104311</v>
-      </c>
       <c r="D10" t="n">
-        <v>6341.6286038549</v>
+        <v>0.259164174612105</v>
       </c>
       <c r="E10" t="n">
+        <v>58766.03389950413</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8079.513828020668</v>
+      </c>
+      <c r="G10" t="n">
         <v>5000</v>
       </c>
-      <c r="F10" t="n">
-        <v>1176.81110778884</v>
-      </c>
-      <c r="G10" t="n">
-        <v>17422.46089039437</v>
-      </c>
       <c r="H10" t="n">
-        <v>36.72535831533005</v>
+        <v>1723.743211925499</v>
       </c>
       <c r="I10" t="n">
-        <v>74.66324541881465</v>
+        <v>16860.90092152725</v>
       </c>
       <c r="J10" t="n">
-        <v>218.5656426435187</v>
+        <v>0.01</v>
       </c>
       <c r="K10" t="n">
-        <v>21.2236566394073</v>
+        <v>0.008382266520494131</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24.09668776487607</v>
+      </c>
+      <c r="M10" t="n">
+        <v>75.29223560645846</v>
+      </c>
+      <c r="N10" t="n">
+        <v>142.6391472776811</v>
+      </c>
+      <c r="O10" t="n">
+        <v>27.03987224906516</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>results/sensitivity/theta/theta_0.9</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_theta.xlsx
+++ b/plot/sensitivity_theta.xlsx
@@ -521,40 +521,40 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3021709655666015</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E2" t="n">
-        <v>31645.82756545992</v>
+        <v>38317.54338179056</v>
       </c>
       <c r="F2" t="n">
-        <v>9779.512720130722</v>
+        <v>8964</v>
       </c>
       <c r="G2" t="n">
         <v>5000</v>
       </c>
       <c r="H2" t="n">
-        <v>860.9664641283048</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>16883.08874442382</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009684058484656543</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4.651018313411994</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M2" t="n">
-        <v>49.20336046873206</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N2" t="n">
-        <v>91.34304614618944</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O2" t="n">
-        <v>32.72929290539064</v>
+        <v>30</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -573,40 +573,40 @@
         <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3017438238319078</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E3" t="n">
-        <v>31641.78122526611</v>
+        <v>38317.54338179056</v>
       </c>
       <c r="F3" t="n">
-        <v>9779.956226864666</v>
+        <v>8964</v>
       </c>
       <c r="G3" t="n">
         <v>5000</v>
       </c>
       <c r="H3" t="n">
-        <v>875.9272304665869</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16868.19242861049</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008813266466412136</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.65102324378649</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M3" t="n">
-        <v>49.20350239966614</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N3" t="n">
-        <v>91.31564821809512</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O3" t="n">
-        <v>32.73077719834226</v>
+        <v>30</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -625,40 +625,40 @@
         <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E4" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F4" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G4" t="n">
         <v>5000</v>
       </c>
       <c r="H4" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M4" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N4" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O4" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -677,40 +677,40 @@
         <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.292247893233171</v>
+        <v>0.3157184983106572</v>
       </c>
       <c r="E5" t="n">
-        <v>37550.12301126753</v>
+        <v>42148.8152894132</v>
       </c>
       <c r="F5" t="n">
-        <v>9502.805537220844</v>
+        <v>8964</v>
       </c>
       <c r="G5" t="n">
         <v>5000</v>
       </c>
       <c r="H5" t="n">
-        <v>1161.446481915717</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>16859.00873225188</v>
+        <v>17912.44955479915</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008273709378654355</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4.676759773541903</v>
+        <v>5.048039932869301</v>
       </c>
       <c r="M5" t="n">
-        <v>61.58552179614139</v>
+        <v>60.63244097394929</v>
       </c>
       <c r="N5" t="n">
-        <v>105.911812211365</v>
+        <v>137.1350602500455</v>
       </c>
       <c r="O5" t="n">
-        <v>31.80323138293456</v>
+        <v>30</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -729,40 +729,40 @@
         <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3020527956578568</v>
+        <v>0.3220164448617141</v>
       </c>
       <c r="E6" t="n">
-        <v>31372.57958274427</v>
+        <v>47559.68145617576</v>
       </c>
       <c r="F6" t="n">
-        <v>9800.026448021676</v>
+        <v>8964</v>
       </c>
       <c r="G6" t="n">
         <v>5000</v>
       </c>
       <c r="H6" t="n">
-        <v>874.611288827379</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>16864.36011021649</v>
+        <v>18419.33289091507</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008588460215499289</v>
+        <v>0.003689164420402339</v>
       </c>
       <c r="L6" t="n">
-        <v>4.639831277408183</v>
+        <v>21.96026008025512</v>
       </c>
       <c r="M6" t="n">
-        <v>48.88131872381109</v>
+        <v>64.94747363362046</v>
       </c>
       <c r="N6" t="n">
-        <v>90.20473226531821</v>
+        <v>96.9285554529103</v>
       </c>
       <c r="O6" t="n">
-        <v>32.79794661319169</v>
+        <v>30</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -781,40 +781,40 @@
         <v>0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2814912660214979</v>
+        <v>0.3367948062344709</v>
       </c>
       <c r="E7" t="n">
-        <v>44285.74422141934</v>
+        <v>60256.47634063246</v>
       </c>
       <c r="F7" t="n">
-        <v>9136.141490533599</v>
+        <v>8964</v>
       </c>
       <c r="G7" t="n">
         <v>5000</v>
       </c>
       <c r="H7" t="n">
-        <v>1433.868536084216</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>16850.90740251968</v>
+        <v>19608.75313356425</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007794040982033943</v>
+        <v>0.03662794059429897</v>
       </c>
       <c r="L7" t="n">
-        <v>11.45342611255706</v>
+        <v>50.72213484344923</v>
       </c>
       <c r="M7" t="n">
-        <v>67.84627905306724</v>
+        <v>65.14972888290964</v>
       </c>
       <c r="N7" t="n">
-        <v>111.2859435006139</v>
+        <v>66.12184513126688</v>
       </c>
       <c r="O7" t="n">
-        <v>30.57610940606961</v>
+        <v>30</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -833,40 +833,40 @@
         <v>0.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2865833899516972</v>
+        <v>0.346005640540451</v>
       </c>
       <c r="E8" t="n">
-        <v>41682.42977334704</v>
+        <v>68169.94326351704</v>
       </c>
       <c r="F8" t="n">
-        <v>9336.169794196723</v>
+        <v>8964</v>
       </c>
       <c r="G8" t="n">
         <v>5000</v>
       </c>
       <c r="H8" t="n">
-        <v>1354.768803431721</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>16886.16011985155</v>
+        <v>20350.07705296821</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009867081164896955</v>
+        <v>0.02734857314774429</v>
       </c>
       <c r="L8" t="n">
-        <v>8.2918222755351</v>
+        <v>70.61540963541685</v>
       </c>
       <c r="M8" t="n">
-        <v>67.54766614801947</v>
+        <v>64.26011078942814</v>
       </c>
       <c r="N8" t="n">
-        <v>107.1205999035996</v>
+        <v>41.08442830292326</v>
       </c>
       <c r="O8" t="n">
-        <v>31.24554817334914</v>
+        <v>30</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -885,40 +885,40 @@
         <v>0.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2936103895698572</v>
+        <v>0.3618488885845292</v>
       </c>
       <c r="E9" t="n">
-        <v>37214.87802743564</v>
+        <v>81781.63306087565</v>
       </c>
       <c r="F9" t="n">
-        <v>9611.246169937953</v>
+        <v>8964</v>
       </c>
       <c r="G9" t="n">
         <v>5000</v>
       </c>
       <c r="H9" t="n">
-        <v>1209.653892624262</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>16887.83661349177</v>
+        <v>21625.2035340189</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009966633872160447</v>
+        <v>0.02845050500558992</v>
       </c>
       <c r="L9" t="n">
-        <v>3.946976159499966</v>
+        <v>98.45308310114862</v>
       </c>
       <c r="M9" t="n">
-        <v>64.17615919701133</v>
+        <v>60.19939884851637</v>
       </c>
       <c r="N9" t="n">
-        <v>101.3856716703093</v>
+        <v>28.59975697087713</v>
       </c>
       <c r="O9" t="n">
-        <v>32.16615184048846</v>
+        <v>30</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -937,40 +937,40 @@
         <v>0.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.259164174612105</v>
+        <v>0.3787788225529746</v>
       </c>
       <c r="E10" t="n">
-        <v>58766.03389950413</v>
+        <v>96326.94654881126</v>
       </c>
       <c r="F10" t="n">
-        <v>8079.513828020668</v>
+        <v>8964</v>
       </c>
       <c r="G10" t="n">
         <v>5000</v>
       </c>
       <c r="H10" t="n">
-        <v>1723.743211925499</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>16860.90092152725</v>
+        <v>22987.79074249683</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008382266520494131</v>
+        <v>0.01941112670710306</v>
       </c>
       <c r="L10" t="n">
-        <v>24.09668776487607</v>
+        <v>110.0179961181225</v>
       </c>
       <c r="M10" t="n">
-        <v>75.29223560645846</v>
+        <v>63.9303687415199</v>
       </c>
       <c r="N10" t="n">
-        <v>142.6391472776811</v>
+        <v>71.84692170321193</v>
       </c>
       <c r="O10" t="n">
-        <v>27.03987224906516</v>
+        <v>30</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>

--- a/plot/sensitivity_theta.xlsx
+++ b/plot/sensitivity_theta.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,55 +456,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Annual Grid Demand Charge (万元/yr)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Annual Grid Energy Cost (万元/yr)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MIP Gap Target</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MIP Gap Achieved</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Wind (MW)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PV (MW)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Storage (MWh)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Grid (MW)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Output Directory</t>
         </is>
@@ -521,42 +531,48 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E2" t="n">
-        <v>38317.54338179056</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F2" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G2" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I2" t="n">
         <v>5000</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.05</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M2" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
-      </c>
-      <c r="P2" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>60</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.1</t>
         </is>
@@ -573,42 +589,48 @@
         <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E3" t="n">
-        <v>38317.54338179056</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F3" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G3" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I3" t="n">
         <v>5000</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.05</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M3" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
-      </c>
-      <c r="P3" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.2</t>
         </is>
@@ -625,42 +647,48 @@
         <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E4" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F4" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G4" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I4" t="n">
         <v>5000</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M4" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
-      </c>
-      <c r="P4" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.3</t>
         </is>
@@ -677,42 +705,48 @@
         <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3157184983106572</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E5" t="n">
-        <v>42148.8152894132</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F5" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G5" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I5" t="n">
         <v>5000</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>17912.44955479915</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.05</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5.048039932869301</v>
-      </c>
       <c r="M5" t="n">
-        <v>60.63244097394929</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>137.1350602500455</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
-      </c>
-      <c r="P5" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.4</t>
         </is>
@@ -729,42 +763,48 @@
         <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3220164448617141</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E6" t="n">
-        <v>47559.68145617576</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F6" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G6" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I6" t="n">
         <v>5000</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>18419.33289091507</v>
-      </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>16830.68287943382</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.05</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.003689164420402339</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21.96026008025512</v>
-      </c>
       <c r="M6" t="n">
-        <v>64.94747363362046</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>96.9285554529103</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
-      </c>
-      <c r="P6" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.5</t>
         </is>
@@ -781,42 +821,48 @@
         <v>0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3367948062344709</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E7" t="n">
-        <v>60256.47634063246</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F7" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G7" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I7" t="n">
         <v>5000</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>19608.75313356425</v>
-      </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.05</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.03662794059429897</v>
-      </c>
-      <c r="L7" t="n">
-        <v>50.72213484344923</v>
-      </c>
       <c r="M7" t="n">
-        <v>65.14972888290964</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>66.12184513126688</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
-      </c>
-      <c r="P7" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.6</t>
         </is>
@@ -833,42 +879,48 @@
         <v>0.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.346005640540451</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E8" t="n">
-        <v>68169.94326351704</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F8" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G8" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I8" t="n">
         <v>5000</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>20350.07705296821</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.05</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.02734857314774429</v>
-      </c>
-      <c r="L8" t="n">
-        <v>70.61540963541685</v>
-      </c>
       <c r="M8" t="n">
-        <v>64.26011078942814</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>41.08442830292326</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
-      </c>
-      <c r="P8" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>60</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.7</t>
         </is>
@@ -885,42 +937,48 @@
         <v>0.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3618488885845292</v>
+        <v>0.3716149739695488</v>
       </c>
       <c r="E9" t="n">
-        <v>81781.63306087565</v>
+        <v>77833.33572278688</v>
       </c>
       <c r="F9" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G9" t="n">
+        <v>3511.863324881522</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7248.663324881521</v>
+      </c>
+      <c r="I9" t="n">
         <v>5000</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>21625.2035340189</v>
-      </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16926.04424290729</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.05</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.02845050500558992</v>
-      </c>
-      <c r="L9" t="n">
-        <v>98.45308310114862</v>
-      </c>
       <c r="M9" t="n">
-        <v>60.19939884851637</v>
+        <v>0.003318444992925108</v>
       </c>
       <c r="N9" t="n">
-        <v>28.59975697087713</v>
+        <v>94.03083678726833</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
-      </c>
-      <c r="P9" t="inlineStr">
+        <v>57.84559778370403</v>
+      </c>
+      <c r="P9" t="n">
+        <v>22.27436210209785</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>60</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.8</t>
         </is>
@@ -937,42 +995,48 @@
         <v>0.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3787788225529746</v>
+        <v>0.3641769668449113</v>
       </c>
       <c r="E10" t="n">
-        <v>96326.94654881126</v>
+        <v>98143.04883617818</v>
       </c>
       <c r="F10" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G10" t="n">
+        <v>1902.268588120597</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5639.068588120596</v>
+      </c>
+      <c r="I10" t="n">
         <v>5000</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>22987.79074249683</v>
-      </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17689.22404696498</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.05</v>
       </c>
-      <c r="K10" t="n">
-        <v>0.01941112670710306</v>
-      </c>
-      <c r="L10" t="n">
-        <v>110.0179961181225</v>
-      </c>
       <c r="M10" t="n">
-        <v>63.9303687415199</v>
+        <v>0.02213370073422277</v>
       </c>
       <c r="N10" t="n">
-        <v>71.84692170321193</v>
+        <v>115.4923181218995</v>
       </c>
       <c r="O10" t="n">
-        <v>30</v>
-      </c>
-      <c r="P10" t="inlineStr">
+        <v>63.04073161875912</v>
+      </c>
+      <c r="P10" t="n">
+        <v>61.43625651607146</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>60</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>results/sensitivity/theta/theta_0.9</t>
         </is>

--- a/plot/sensitivity_theta.xlsx
+++ b/plot/sensitivity_theta.xlsx
@@ -531,19 +531,19 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.5467008614374381</v>
       </c>
       <c r="E2" t="n">
-        <v>67074.19337427949</v>
+        <v>11538.16715091549</v>
       </c>
       <c r="F2" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G2" t="n">
-        <v>4673.487665886038</v>
+        <v>12371.72658893182</v>
       </c>
       <c r="H2" t="n">
-        <v>8410.287665886037</v>
+        <v>17685.32658893181</v>
       </c>
       <c r="I2" t="n">
         <v>5000</v>
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>16830.68287943381</v>
+        <v>19617.4731312491</v>
       </c>
       <c r="L2" t="n">
         <v>0.05</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>57.92667956937272</v>
+        <v>27.04541787728873</v>
       </c>
       <c r="P2" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>60</v>
@@ -589,19 +589,19 @@
         <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.5276871004846422</v>
       </c>
       <c r="E3" t="n">
-        <v>67074.19337427949</v>
+        <v>22356.33430183098</v>
       </c>
       <c r="F3" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4673.487665886038</v>
+        <v>10997.09030127273</v>
       </c>
       <c r="H3" t="n">
-        <v>8410.287665886037</v>
+        <v>16310.69030127273</v>
       </c>
       <c r="I3" t="n">
         <v>5000</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>16830.68287943381</v>
+        <v>19506.71838887327</v>
       </c>
       <c r="L3" t="n">
         <v>0.05</v>
@@ -619,13 +619,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>57.92667956937272</v>
+        <v>54.09083575457745</v>
       </c>
       <c r="P3" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>60</v>
@@ -647,19 +647,19 @@
         <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.5086733395318465</v>
       </c>
       <c r="E4" t="n">
-        <v>67074.19337427949</v>
+        <v>33174.50145274647</v>
       </c>
       <c r="F4" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G4" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613662</v>
       </c>
       <c r="H4" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361366</v>
       </c>
       <c r="I4" t="n">
         <v>5000</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>16830.68287943381</v>
+        <v>19395.96364649746</v>
       </c>
       <c r="L4" t="n">
         <v>0.05</v>
@@ -677,13 +677,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>57.92667956937272</v>
+        <v>81.13625363186617</v>
       </c>
       <c r="P4" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>60</v>
@@ -705,19 +705,19 @@
         <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.4896595785790503</v>
       </c>
       <c r="E5" t="n">
-        <v>67074.19337427949</v>
+        <v>43992.66860366196</v>
       </c>
       <c r="F5" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G5" t="n">
-        <v>4673.487665886038</v>
+        <v>8247.817725954574</v>
       </c>
       <c r="H5" t="n">
-        <v>8410.287665886037</v>
+        <v>13561.41772595457</v>
       </c>
       <c r="I5" t="n">
         <v>5000</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>16830.68287943381</v>
+        <v>19285.20890412163</v>
       </c>
       <c r="L5" t="n">
         <v>0.05</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>57.92667956937272</v>
+        <v>108.1816715091549</v>
       </c>
       <c r="P5" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>60</v>
@@ -763,19 +763,19 @@
         <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.4799210745767064</v>
       </c>
       <c r="E6" t="n">
-        <v>67074.19337427949</v>
+        <v>59592.12504762268</v>
       </c>
       <c r="F6" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G6" t="n">
-        <v>4673.487665886038</v>
+        <v>6873.181438295484</v>
       </c>
       <c r="H6" t="n">
-        <v>8410.287665886037</v>
+        <v>12186.78143829548</v>
       </c>
       <c r="I6" t="n">
         <v>5000</v>
@@ -784,22 +784,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>16830.68287943382</v>
+        <v>19733.05001405974</v>
       </c>
       <c r="L6" t="n">
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.001258818558995416</v>
       </c>
       <c r="N6" t="n">
-        <v>79.39508302539429</v>
+        <v>10.36861624743512</v>
       </c>
       <c r="O6" t="n">
-        <v>57.92667956937272</v>
+        <v>126.4430801241865</v>
       </c>
       <c r="P6" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>60</v>
@@ -821,19 +821,19 @@
         <v>0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.4826258429308134</v>
       </c>
       <c r="E7" t="n">
-        <v>67074.19337427949</v>
+        <v>81605.94663598404</v>
       </c>
       <c r="F7" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G7" t="n">
-        <v>4673.487665886038</v>
+        <v>5498.545150636408</v>
       </c>
       <c r="H7" t="n">
-        <v>8410.287665886037</v>
+        <v>10812.14515063641</v>
       </c>
       <c r="I7" t="n">
         <v>5000</v>
@@ -842,22 +842,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>16830.68287943381</v>
+        <v>20930.27848487164</v>
       </c>
       <c r="L7" t="n">
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.001280989970660474</v>
       </c>
       <c r="N7" t="n">
-        <v>79.39508302539429</v>
+        <v>34.6473070745355</v>
       </c>
       <c r="O7" t="n">
-        <v>57.92667956937272</v>
+        <v>132.9202524408891</v>
       </c>
       <c r="P7" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>60</v>
@@ -879,19 +879,19 @@
         <v>0.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.4863288047835518</v>
       </c>
       <c r="E8" t="n">
-        <v>67074.19337427949</v>
+        <v>104134.325601342</v>
       </c>
       <c r="F8" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4673.487665886038</v>
+        <v>4123.908862977329</v>
       </c>
       <c r="H8" t="n">
-        <v>8410.287665886037</v>
+        <v>9437.508862977329</v>
       </c>
       <c r="I8" t="n">
         <v>5000</v>
@@ -900,22 +900,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16830.68287943381</v>
+        <v>22187.62245988155</v>
       </c>
       <c r="L8" t="n">
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.00158884791637334</v>
       </c>
       <c r="N8" t="n">
-        <v>79.39508302539429</v>
+        <v>60.04185758975919</v>
       </c>
       <c r="O8" t="n">
-        <v>57.92667956937272</v>
+        <v>138.4520988238367</v>
       </c>
       <c r="P8" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>60</v>
@@ -937,19 +937,19 @@
         <v>0.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3716149739695488</v>
+        <v>0.4935702201578174</v>
       </c>
       <c r="E9" t="n">
-        <v>77833.33572278688</v>
+        <v>128120.0353244798</v>
       </c>
       <c r="F9" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3511.863324881522</v>
+        <v>2773.719356788423</v>
       </c>
       <c r="H9" t="n">
-        <v>7248.663324881521</v>
+        <v>8087.319356788424</v>
       </c>
       <c r="I9" t="n">
         <v>5000</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>16926.04424290729</v>
+        <v>23639.67250561429</v>
       </c>
       <c r="L9" t="n">
         <v>0.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003318444992925108</v>
+        <v>0.004991405504281647</v>
       </c>
       <c r="N9" t="n">
-        <v>94.03083678726833</v>
+        <v>85.88856832738061</v>
       </c>
       <c r="O9" t="n">
-        <v>57.84559778370403</v>
+        <v>143.6008873824051</v>
       </c>
       <c r="P9" t="n">
-        <v>22.27436210209785</v>
+        <v>8.325504730755236</v>
       </c>
       <c r="Q9" t="n">
         <v>60</v>
@@ -995,19 +995,19 @@
         <v>0.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3641769668449113</v>
+        <v>0.5082321135735739</v>
       </c>
       <c r="E10" t="n">
-        <v>98143.04883617818</v>
+        <v>154371.0111059207</v>
       </c>
       <c r="F10" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1902.268588120597</v>
+        <v>1527.523573069586</v>
       </c>
       <c r="H10" t="n">
-        <v>5639.068588120596</v>
+        <v>6841.123573069586</v>
       </c>
       <c r="I10" t="n">
         <v>5000</v>
@@ -1016,22 +1016,22 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>17689.22404696498</v>
+        <v>25460.36627656769</v>
       </c>
       <c r="L10" t="n">
         <v>0.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02213370073422277</v>
+        <v>0.01195831352600016</v>
       </c>
       <c r="N10" t="n">
-        <v>115.4923181218995</v>
+        <v>108.2546081565674</v>
       </c>
       <c r="O10" t="n">
-        <v>63.04073161875912</v>
+        <v>151.6984055273463</v>
       </c>
       <c r="P10" t="n">
-        <v>61.43625651607146</v>
+        <v>42.45308246485476</v>
       </c>
       <c r="Q10" t="n">
         <v>60</v>
